--- a/sim_out/rootedfull1/EdgeAnalysis_full_outgroup.xlsx
+++ b/sim_out/rootedfull1/EdgeAnalysis_full_outgroup.xlsx
@@ -20,7 +20,7 @@
     <t xml:space="preserve"># of branches</t>
   </si>
   <si>
-    <t xml:space="preserve">RF dist vs True Tree</t>
+    <t xml:space="preserve">Jaccard dist vs True Tree (for Majority we use RF)</t>
   </si>
   <si>
     <t xml:space="preserve">Extended</t>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">Majority</t>
   </si>
   <si>
-    <t xml:space="preserve">AVG RF to bootstrap</t>
+    <t xml:space="preserve">AVG Jaccard to bootstrap (for Majority we use RF)</t>
   </si>
   <si>
     <t xml:space="preserve">Network</t>
